--- a/output/yearly_benthic_cover_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_64_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.28430022058134</v>
+        <v>45.48458050636022</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1005032026166</v>
+        <v>100.3837344546863</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93851432873254</v>
+        <v>87.92719477770257</v>
       </c>
       <c r="C3" t="n">
-        <v>45.83165694778494</v>
+        <v>45.82435935802696</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228576280430265</v>
+        <v>2.228552734771521</v>
       </c>
       <c r="E3" t="n">
-        <v>5.646295879156056</v>
+        <v>5.641517918995996</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428587601434217</v>
+        <v>0.7428509115905071</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94032889970795</v>
+        <v>33.93791233734361</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17150296659739</v>
+        <v>34.17114193316332</v>
       </c>
       <c r="I3" t="n">
-        <v>6.566084291801064</v>
+        <v>6.562400744396946</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642867250896385</v>
+        <v>4.642818197440669</v>
       </c>
       <c r="K3" t="n">
-        <v>12.06148567126746</v>
+        <v>12.07280522229742</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87115230414284</v>
+        <v>48.86726008355705</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7642949231952</v>
+        <v>106.7644246638814</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07279517410095</v>
+        <v>86.94369783260481</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60429681644514</v>
+        <v>42.47878150543678</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187018193714547</v>
+        <v>2.180700067710002</v>
       </c>
       <c r="E4" t="n">
-        <v>6.454875210992411</v>
+        <v>6.433739778498679</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444180914052493</v>
+        <v>0.7444116686635567</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30741579551673</v>
+        <v>33.2091794720617</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24323220464147</v>
+        <v>34.24293675852361</v>
       </c>
       <c r="I4" t="n">
-        <v>5.483222606547756</v>
+        <v>5.480157158000052</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652613071282808</v>
+        <v>4.65257292914723</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92720482589904</v>
+        <v>13.05630216739519</v>
       </c>
       <c r="L4" t="n">
-        <v>44.286107127328</v>
+        <v>44.28262741760144</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81760876967219</v>
+        <v>99.81771109043341</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.93966599103683</v>
+        <v>85.78638021000921</v>
       </c>
       <c r="C5" t="n">
-        <v>42.32215680391866</v>
+        <v>42.17184630294943</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131720818344288</v>
+        <v>2.124126297565454</v>
       </c>
       <c r="E5" t="n">
-        <v>7.054578573170656</v>
+        <v>7.029315614014596</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457397735469395</v>
+        <v>0.7457349636736421</v>
       </c>
       <c r="G5" t="n">
-        <v>32.46525879876594</v>
+        <v>32.34763573481847</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30402958315922</v>
+        <v>34.30380832898754</v>
       </c>
       <c r="I5" t="n">
-        <v>4.577464859381426</v>
+        <v>4.574915747989234</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660873584668372</v>
+        <v>4.660843522960263</v>
       </c>
       <c r="K5" t="n">
-        <v>14.06033400896317</v>
+        <v>14.21361978999082</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46519744804741</v>
+        <v>43.46230731933754</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84768826092923</v>
+        <v>99.84777341227777</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.60281208385885</v>
+        <v>84.39905024716018</v>
       </c>
       <c r="C6" t="n">
-        <v>41.69620306489725</v>
+        <v>41.49488761222167</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066406482600788</v>
+        <v>2.0562154452765</v>
       </c>
       <c r="E6" t="n">
-        <v>7.475147493428763</v>
+        <v>7.440943153410924</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468622525598457</v>
+        <v>0.7468595219406076</v>
       </c>
       <c r="G6" t="n">
-        <v>31.47054748622681</v>
+        <v>31.31344322244199</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3556636177529</v>
+        <v>34.35553800926795</v>
       </c>
       <c r="I6" t="n">
-        <v>3.820295672790702</v>
+        <v>3.8181788826934</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667889078499035</v>
+        <v>4.667872012128798</v>
       </c>
       <c r="K6" t="n">
-        <v>15.39718791614116</v>
+        <v>15.60094975283983</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77945721731211</v>
+        <v>42.77708164193883</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87284819835051</v>
+        <v>99.87291900700032</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.13572712472785</v>
+        <v>82.84077308981495</v>
       </c>
       <c r="C7" t="n">
-        <v>40.82247537690614</v>
+        <v>40.52948680832112</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995033564598869</v>
+        <v>1.980237957535159</v>
       </c>
       <c r="E7" t="n">
-        <v>7.748233426714383</v>
+        <v>7.696981556513845</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478168098514518</v>
+        <v>0.7478169473087891</v>
       </c>
       <c r="G7" t="n">
-        <v>30.38356637959433</v>
+        <v>30.15640651501062</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39957325316678</v>
+        <v>34.3995795762043</v>
       </c>
       <c r="I7" t="n">
-        <v>3.187648629230471</v>
+        <v>3.185894616562314</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673855061571573</v>
+        <v>4.673855920679932</v>
       </c>
       <c r="K7" t="n">
-        <v>16.86427287527215</v>
+        <v>17.15922691018504</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20713242357753</v>
+        <v>42.20522575697458</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89388067575581</v>
+        <v>99.89393947548074</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.0113942064953</v>
+        <v>87.78691699593421</v>
       </c>
       <c r="C8" t="n">
-        <v>43.16404498810989</v>
+        <v>42.82639646168657</v>
       </c>
       <c r="D8" t="n">
-        <v>1.999264539984688</v>
+        <v>1.984531015068319</v>
       </c>
       <c r="E8" t="n">
-        <v>9.605249749225971</v>
+        <v>9.530744644954662</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494027453323014</v>
+        <v>0.7494381773063522</v>
       </c>
       <c r="G8" t="n">
-        <v>30.90166827405963</v>
+        <v>30.65452812469135</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47252628528587</v>
+        <v>34.4741561560922</v>
       </c>
       <c r="I8" t="n">
-        <v>5.599515454279958</v>
+        <v>5.70953026965662</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683767158326884</v>
+        <v>4.683988608164701</v>
       </c>
       <c r="K8" t="n">
-        <v>11.98860579350472</v>
+        <v>12.21308300406579</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66109370536452</v>
+        <v>44.77061456530043</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81374448697912</v>
+        <v>99.81009403105278</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.98335820742309</v>
+        <v>85.91948664253464</v>
       </c>
       <c r="C9" t="n">
-        <v>42.0052597892915</v>
+        <v>41.84480192385121</v>
       </c>
       <c r="D9" t="n">
-        <v>1.907326837472032</v>
+        <v>1.900156337516293</v>
       </c>
       <c r="E9" t="n">
-        <v>9.942664915484865</v>
+        <v>9.919990587935036</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750760856012526</v>
+        <v>0.7508241172757515</v>
       </c>
       <c r="G9" t="n">
-        <v>29.48063152374191</v>
+        <v>29.35121469376403</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5349993765762</v>
+        <v>34.53790939468457</v>
       </c>
       <c r="I9" t="n">
-        <v>4.674719348057288</v>
+        <v>4.766740778385506</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692255350078287</v>
+        <v>4.692650732973447</v>
       </c>
       <c r="K9" t="n">
-        <v>14.01664179257691</v>
+        <v>14.08051335746534</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82255632217938</v>
+        <v>43.91608665563742</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8444579040478</v>
+        <v>99.84140193695399</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.7800065019308</v>
+        <v>83.98972465684456</v>
       </c>
       <c r="C10" t="n">
-        <v>40.5272990033381</v>
+        <v>40.65447108113235</v>
       </c>
       <c r="D10" t="n">
-        <v>1.808449470907886</v>
+        <v>1.813952918073348</v>
       </c>
       <c r="E10" t="n">
-        <v>10.07750357850546</v>
+        <v>10.13304814854481</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519262906516699</v>
+        <v>0.7520096575026477</v>
       </c>
       <c r="G10" t="n">
-        <v>27.95233173135865</v>
+        <v>28.01965316829836</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58860936997682</v>
+        <v>34.59244424512179</v>
       </c>
       <c r="I10" t="n">
-        <v>3.901646743957375</v>
+        <v>3.978556159912079</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699539316572936</v>
+        <v>4.700060359391548</v>
       </c>
       <c r="K10" t="n">
-        <v>16.21999349806921</v>
+        <v>16.01027534315542</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12285418336889</v>
+        <v>43.20284410964594</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8701466847762</v>
+        <v>99.86759053393371</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.50153929193877</v>
+        <v>81.95011362716886</v>
       </c>
       <c r="C11" t="n">
-        <v>38.85363924253685</v>
+        <v>39.23163010717569</v>
       </c>
       <c r="D11" t="n">
-        <v>1.707289311667557</v>
+        <v>1.72370632552448</v>
       </c>
       <c r="E11" t="n">
-        <v>10.05641006955741</v>
+        <v>10.18223884124856</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529275182308811</v>
+        <v>0.7530251645031195</v>
       </c>
       <c r="G11" t="n">
-        <v>26.38874791297129</v>
+        <v>26.62563781230676</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63466583862053</v>
+        <v>34.63915756714349</v>
       </c>
       <c r="I11" t="n">
-        <v>3.255701651948106</v>
+        <v>3.319940638297969</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705796988943006</v>
+        <v>4.706407278144497</v>
       </c>
       <c r="K11" t="n">
-        <v>18.49846070806121</v>
+        <v>18.04988637283112</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5395209731809</v>
+        <v>42.60796807110674</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89162092377897</v>
+        <v>99.88948455111355</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.20182162942413</v>
+        <v>79.75999405126097</v>
       </c>
       <c r="C12" t="n">
-        <v>37.05783793490527</v>
+        <v>37.55559143410531</v>
       </c>
       <c r="D12" t="n">
-        <v>1.606212962903394</v>
+        <v>1.627613444742473</v>
       </c>
       <c r="E12" t="n">
-        <v>9.913739888705056</v>
+        <v>10.07623778191411</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537882271015531</v>
+        <v>0.7538968395774642</v>
       </c>
       <c r="G12" t="n">
-        <v>24.82645951271424</v>
+        <v>25.14131638112306</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67425844667144</v>
+        <v>34.67925462056335</v>
       </c>
       <c r="I12" t="n">
-        <v>2.716186171943736</v>
+        <v>2.769819735981368</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711176419384707</v>
+        <v>4.711855247359152</v>
       </c>
       <c r="K12" t="n">
-        <v>20.79817837057587</v>
+        <v>20.24000594873901</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05354753752029</v>
+        <v>42.11218204386963</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90956384300142</v>
+        <v>99.90777942671396</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.90679963880676</v>
+        <v>77.46582135516219</v>
       </c>
       <c r="C13" t="n">
-        <v>35.18242668024347</v>
+        <v>35.68958893681129</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5062695664864</v>
+        <v>1.527787131150814</v>
       </c>
       <c r="E13" t="n">
-        <v>9.674495750099682</v>
+        <v>9.84331216891664</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545284592096476</v>
+        <v>0.7546463580746816</v>
       </c>
       <c r="G13" t="n">
-        <v>23.28168261076187</v>
+        <v>23.59932559622499</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70830912364379</v>
+        <v>34.71373247143535</v>
       </c>
       <c r="I13" t="n">
-        <v>2.265711258545068</v>
+        <v>2.310477891392969</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715802870060298</v>
+        <v>4.716539737966761</v>
       </c>
       <c r="K13" t="n">
-        <v>23.09320036119327</v>
+        <v>22.5341786448378</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64892334267593</v>
+        <v>41.69929298124031</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92455038411266</v>
+        <v>99.92306056288939</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.72427239973102</v>
+        <v>83.80673920688776</v>
       </c>
       <c r="C14" t="n">
-        <v>39.40628586081568</v>
+        <v>39.73208938417603</v>
       </c>
       <c r="D14" t="n">
-        <v>1.508038669974343</v>
+        <v>1.529478219423739</v>
       </c>
       <c r="E14" t="n">
-        <v>12.02880726427511</v>
+        <v>12.09184588253637</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554146478166803</v>
+        <v>0.7554816665939935</v>
       </c>
       <c r="G14" t="n">
-        <v>25.16030769679366</v>
+        <v>25.39926256337347</v>
       </c>
       <c r="H14" t="n">
-        <v>36.60035470576018</v>
+        <v>36.52597183513107</v>
       </c>
       <c r="I14" t="n">
-        <v>2.950007866256784</v>
+        <v>2.782938623616649</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721341548854252</v>
+        <v>4.72176041621246</v>
       </c>
       <c r="K14" t="n">
-        <v>16.27572760026898</v>
+        <v>16.19326079311225</v>
       </c>
       <c r="L14" t="n">
-        <v>44.2197683000353</v>
+        <v>43.98198776838171</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90178176111995</v>
+        <v>99.90733794566998</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.08229775844697</v>
+        <v>83.14221382083717</v>
       </c>
       <c r="C15" t="n">
-        <v>39.22031695233365</v>
+        <v>39.49806219915709</v>
       </c>
       <c r="D15" t="n">
-        <v>1.484484900516176</v>
+        <v>1.504830176278577</v>
       </c>
       <c r="E15" t="n">
-        <v>12.25105943585338</v>
+        <v>12.28386078530893</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561604542668385</v>
+        <v>0.7561847509884593</v>
       </c>
       <c r="G15" t="n">
-        <v>24.76733363134951</v>
+        <v>24.98994511669992</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63648953673881</v>
+        <v>36.55996450752212</v>
       </c>
       <c r="I15" t="n">
-        <v>2.46076696055454</v>
+        <v>2.321273790361286</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72600283916774</v>
+        <v>4.726154693677871</v>
       </c>
       <c r="K15" t="n">
-        <v>16.91770224155302</v>
+        <v>16.85778617916283</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78003614316175</v>
+        <v>43.56684777102407</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91805533704841</v>
+        <v>99.92269614934399</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.76918235751701</v>
+        <v>80.82140151790588</v>
       </c>
       <c r="C16" t="n">
-        <v>37.28769621002181</v>
+        <v>37.53640766389478</v>
       </c>
       <c r="D16" t="n">
-        <v>1.396484188327309</v>
+        <v>1.415899159849612</v>
       </c>
       <c r="E16" t="n">
-        <v>11.86687561640878</v>
+        <v>11.88057746846768</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568009318855373</v>
+        <v>0.756788521678189</v>
       </c>
       <c r="G16" t="n">
-        <v>23.2991186311025</v>
+        <v>23.51311320917658</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66752111402319</v>
+        <v>36.58915556824948</v>
       </c>
       <c r="I16" t="n">
-        <v>2.052376051485092</v>
+        <v>1.935939329995665</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730005824284607</v>
+        <v>4.729928260488682</v>
       </c>
       <c r="K16" t="n">
-        <v>19.23081764248301</v>
+        <v>19.17859848209412</v>
       </c>
       <c r="L16" t="n">
-        <v>43.413131509702</v>
+        <v>43.22051402650106</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93164536220681</v>
+        <v>99.93552017248996</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.48502209013731</v>
+        <v>82.34416092953199</v>
       </c>
       <c r="C17" t="n">
-        <v>38.53257814207785</v>
+        <v>38.66905005648819</v>
       </c>
       <c r="D17" t="n">
-        <v>1.397642498194571</v>
+        <v>1.416988821471424</v>
       </c>
       <c r="E17" t="n">
-        <v>12.6549135554069</v>
+        <v>12.59990886754039</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574286582817851</v>
+        <v>0.7573709384429455</v>
       </c>
       <c r="G17" t="n">
-        <v>23.75455416834405</v>
+        <v>23.92454073745973</v>
       </c>
       <c r="H17" t="n">
-        <v>37.13404503496069</v>
+        <v>37.01064628600821</v>
       </c>
       <c r="I17" t="n">
-        <v>2.052509060688163</v>
+        <v>1.901136913340878</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733929114261155</v>
+        <v>4.73356836526841</v>
       </c>
       <c r="K17" t="n">
-        <v>17.51497790986269</v>
+        <v>17.65583907046802</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88408368060072</v>
+        <v>43.61178837495091</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93163973254127</v>
+        <v>99.93667750190711</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.28184279712887</v>
+        <v>80.09567397997256</v>
       </c>
       <c r="C18" t="n">
-        <v>36.64643029009222</v>
+        <v>36.71436920887464</v>
       </c>
       <c r="D18" t="n">
-        <v>1.317131386184541</v>
+        <v>1.333894651422908</v>
       </c>
       <c r="E18" t="n">
-        <v>12.21120131829085</v>
+        <v>12.12525391354062</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579669472968161</v>
+        <v>0.7578706241269774</v>
       </c>
       <c r="G18" t="n">
-        <v>22.38617450482753</v>
+        <v>22.52157281968408</v>
       </c>
       <c r="H18" t="n">
-        <v>37.16043543926798</v>
+        <v>37.03506455870284</v>
       </c>
       <c r="I18" t="n">
-        <v>1.711639780656065</v>
+        <v>1.585326011701538</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737293420605099</v>
+        <v>4.73669140079361</v>
       </c>
       <c r="K18" t="n">
-        <v>19.71815720287113</v>
+        <v>19.90432602002745</v>
       </c>
       <c r="L18" t="n">
-        <v>43.57839836646198</v>
+        <v>43.32849541239402</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94298585942532</v>
+        <v>99.94719064129609</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.44115260302824</v>
+        <v>79.18734136904931</v>
       </c>
       <c r="C19" t="n">
-        <v>36.06951170981245</v>
+        <v>36.05044356614323</v>
       </c>
       <c r="D19" t="n">
-        <v>1.287070161471817</v>
+        <v>1.300943974231388</v>
       </c>
       <c r="E19" t="n">
-        <v>12.17037207663786</v>
+        <v>12.04603519756494</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584208623703491</v>
+        <v>0.7582923176967007</v>
       </c>
       <c r="G19" t="n">
-        <v>21.87524914893174</v>
+        <v>21.96523122626433</v>
       </c>
       <c r="H19" t="n">
-        <v>37.18268928799461</v>
+        <v>37.05567157008646</v>
       </c>
       <c r="I19" t="n">
-        <v>1.427220675807188</v>
+        <v>1.321840097601115</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740130389814681</v>
+        <v>4.73932698560438</v>
       </c>
       <c r="K19" t="n">
-        <v>20.55884739697176</v>
+        <v>20.81265863095068</v>
       </c>
       <c r="L19" t="n">
-        <v>43.32409534375313</v>
+        <v>43.09286096924773</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95245445053733</v>
+        <v>99.95596316634165</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.94245743356447</v>
+        <v>76.72988942064093</v>
       </c>
       <c r="C20" t="n">
-        <v>33.79064217381011</v>
+        <v>33.79663966979359</v>
       </c>
       <c r="D20" t="n">
-        <v>1.196666342031772</v>
+        <v>1.210988009286151</v>
       </c>
       <c r="E20" t="n">
-        <v>11.51385231821094</v>
+        <v>11.39676857784147</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588118442913206</v>
+        <v>0.7586553592853087</v>
       </c>
       <c r="G20" t="n">
-        <v>20.33873145668368</v>
+        <v>20.44640827205429</v>
       </c>
       <c r="H20" t="n">
-        <v>37.2018577470996</v>
+        <v>37.07341241957126</v>
       </c>
       <c r="I20" t="n">
-        <v>1.189963698426405</v>
+        <v>1.102060787069284</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742574026820753</v>
+        <v>4.741595995533181</v>
       </c>
       <c r="K20" t="n">
-        <v>23.05754256643553</v>
+        <v>23.27011057935905</v>
       </c>
       <c r="L20" t="n">
-        <v>43.11217024098195</v>
+        <v>42.89653197035843</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9603549812276</v>
+        <v>99.96328221951107</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.50800480389374</v>
+        <v>82.09215611132886</v>
       </c>
       <c r="C21" t="n">
-        <v>37.23783098225624</v>
+        <v>37.16411525885756</v>
       </c>
       <c r="D21" t="n">
-        <v>1.197486668785327</v>
+        <v>1.211732455458633</v>
       </c>
       <c r="E21" t="n">
-        <v>13.37920541777587</v>
+        <v>13.20661617879936</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593320174046795</v>
+        <v>0.759121737213184</v>
       </c>
       <c r="G21" t="n">
-        <v>21.92733378410041</v>
+        <v>22.00949126005562</v>
       </c>
       <c r="H21" t="n">
-        <v>38.80201991635253</v>
+        <v>38.64671673883478</v>
       </c>
       <c r="I21" t="n">
-        <v>1.696801890695664</v>
+        <v>1.513966883384887</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745825108779246</v>
+        <v>4.744510857582402</v>
       </c>
       <c r="K21" t="n">
-        <v>17.49199519610627</v>
+        <v>17.90784388867113</v>
       </c>
       <c r="L21" t="n">
-        <v>45.21365250454281</v>
+        <v>44.87760629397405</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94347868290532</v>
+        <v>99.94956544150274</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_64_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.48458050636022</v>
+        <v>45.71413580552456</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3837344546863</v>
+        <v>99.54154433379179</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.92719477770257</v>
+        <v>88.12228768149052</v>
       </c>
       <c r="C3" t="n">
-        <v>45.82435935802696</v>
+        <v>45.9582034769162</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228552734771521</v>
+        <v>2.228951652950608</v>
       </c>
       <c r="E3" t="n">
-        <v>5.641517918995996</v>
+        <v>5.728456045212723</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428509115905071</v>
+        <v>0.7429838843168693</v>
       </c>
       <c r="G3" t="n">
-        <v>33.93791233734361</v>
+        <v>33.98236408690011</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17114193316332</v>
+        <v>34.17725867857599</v>
       </c>
       <c r="I3" t="n">
-        <v>6.562400744396946</v>
+        <v>6.618624056553783</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642818197440669</v>
+        <v>4.643649276980433</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07280522229742</v>
+        <v>11.8777123185095</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86726008355705</v>
+        <v>48.92653310120095</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7644246638814</v>
+        <v>106.7624488966266</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.94369783260481</v>
+        <v>87.38164883897515</v>
       </c>
       <c r="C4" t="n">
-        <v>42.47878150543678</v>
+        <v>42.86137016805299</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180700067710002</v>
+        <v>2.194205899423028</v>
       </c>
       <c r="E4" t="n">
-        <v>6.433739778498679</v>
+        <v>6.560350199368851</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444116686635567</v>
+        <v>0.7445504156569606</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2091794720617</v>
+        <v>33.45263395781235</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24293675852361</v>
+        <v>34.24931912022019</v>
       </c>
       <c r="I4" t="n">
-        <v>5.480157158000052</v>
+        <v>5.527149148637766</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65257292914723</v>
+        <v>4.653440097856003</v>
       </c>
       <c r="K4" t="n">
-        <v>13.05630216739519</v>
+        <v>12.61835116102484</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28262741760144</v>
+        <v>44.33642800268458</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81771109043341</v>
+        <v>99.81614933176242</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.78638021000921</v>
+        <v>86.38582301176038</v>
       </c>
       <c r="C5" t="n">
-        <v>42.17184630294943</v>
+        <v>42.72357424902388</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124126297565454</v>
+        <v>2.146250849089668</v>
       </c>
       <c r="E5" t="n">
-        <v>7.029315614014596</v>
+        <v>7.185998091760021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457349636736421</v>
+        <v>0.7458760473199801</v>
       </c>
       <c r="G5" t="n">
-        <v>32.34763573481847</v>
+        <v>32.72151626933463</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30380832898754</v>
+        <v>34.31029817671909</v>
       </c>
       <c r="I5" t="n">
-        <v>4.574915747989234</v>
+        <v>4.614158281787122</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660843522960263</v>
+        <v>4.661725295749875</v>
       </c>
       <c r="K5" t="n">
-        <v>14.21361978999082</v>
+        <v>13.61417698823961</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46230731933754</v>
+        <v>43.50871684194099</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84777341227777</v>
+        <v>99.8464680792045</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.39905024716018</v>
+        <v>85.22453317163421</v>
       </c>
       <c r="C6" t="n">
-        <v>41.49488761222167</v>
+        <v>42.27920673429298</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0562154452765</v>
+        <v>2.090126789959931</v>
       </c>
       <c r="E6" t="n">
-        <v>7.440943153410924</v>
+        <v>7.639906147928182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468595219406076</v>
+        <v>0.7469994763804996</v>
       </c>
       <c r="G6" t="n">
-        <v>31.31344322244199</v>
+        <v>31.86585472600025</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35553800926795</v>
+        <v>34.36197591350298</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8181788826934</v>
+        <v>3.850923390484236</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667872012128798</v>
+        <v>4.668746727378122</v>
       </c>
       <c r="K6" t="n">
-        <v>15.60094975283983</v>
+        <v>14.7754668283658</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77708164193883</v>
+        <v>42.81715537395823</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87291900700032</v>
+        <v>99.87182893661702</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.84077308981495</v>
+        <v>83.87106773568762</v>
       </c>
       <c r="C7" t="n">
-        <v>40.52948680832112</v>
+        <v>41.52427217522285</v>
       </c>
       <c r="D7" t="n">
-        <v>1.980237957535159</v>
+        <v>2.024699642210425</v>
       </c>
       <c r="E7" t="n">
-        <v>7.696981556513845</v>
+        <v>7.936287995266506</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478169473087891</v>
+        <v>0.7479534245109136</v>
       </c>
       <c r="G7" t="n">
-        <v>30.15640651501062</v>
+        <v>30.86835926527641</v>
       </c>
       <c r="H7" t="n">
-        <v>34.3995795762043</v>
+        <v>34.40585752750203</v>
       </c>
       <c r="I7" t="n">
-        <v>3.185894616562314</v>
+        <v>3.213200977728125</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673855920679932</v>
+        <v>4.67470890319321</v>
       </c>
       <c r="K7" t="n">
-        <v>17.15922691018504</v>
+        <v>16.1289322643124</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20522575697458</v>
+        <v>42.23982546628463</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89393947548074</v>
+        <v>99.89302990581987</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.78691699593421</v>
+        <v>88.63978639590285</v>
       </c>
       <c r="C8" t="n">
-        <v>42.82639646168657</v>
+        <v>43.77906414573303</v>
       </c>
       <c r="D8" t="n">
-        <v>1.984531015068319</v>
+        <v>2.028967640848737</v>
       </c>
       <c r="E8" t="n">
-        <v>9.530744644954662</v>
+        <v>9.735370270709634</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494381773063522</v>
+        <v>0.7495300851329544</v>
       </c>
       <c r="G8" t="n">
-        <v>30.65452812469135</v>
+        <v>31.35748094144507</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4741561560922</v>
+        <v>34.4783839161159</v>
       </c>
       <c r="I8" t="n">
-        <v>5.70953026965662</v>
+        <v>5.605490509569599</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683988608164701</v>
+        <v>4.684563032080964</v>
       </c>
       <c r="K8" t="n">
-        <v>12.21308300406579</v>
+        <v>11.36021360409715</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77061456530043</v>
+        <v>44.67426561083195</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81009403105278</v>
+        <v>99.81354336066212</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.91948664253464</v>
+        <v>86.77864147458159</v>
       </c>
       <c r="C9" t="n">
-        <v>41.84480192385121</v>
+        <v>42.78874436536648</v>
       </c>
       <c r="D9" t="n">
-        <v>1.900156337516293</v>
+        <v>1.944886793994464</v>
       </c>
       <c r="E9" t="n">
-        <v>9.919990587935036</v>
+        <v>10.11187427885109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508241172757515</v>
+        <v>0.7508773944211348</v>
       </c>
       <c r="G9" t="n">
-        <v>29.35121469376403</v>
+        <v>30.05802031935722</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53790939468457</v>
+        <v>34.5403601433722</v>
       </c>
       <c r="I9" t="n">
-        <v>4.766740778385506</v>
+        <v>4.679638829453395</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692650732973447</v>
+        <v>4.692983715132092</v>
       </c>
       <c r="K9" t="n">
-        <v>14.08051335746534</v>
+        <v>13.2213585254184</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91608665563742</v>
+        <v>43.83418903950487</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84140193695399</v>
+        <v>99.84429193028974</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.98972465684456</v>
+        <v>84.63494565528157</v>
       </c>
       <c r="C10" t="n">
-        <v>40.65447108113235</v>
+        <v>41.37191280474796</v>
       </c>
       <c r="D10" t="n">
-        <v>1.813952918073348</v>
+        <v>1.848729032441617</v>
       </c>
       <c r="E10" t="n">
-        <v>10.13304814854481</v>
+        <v>10.26287953699524</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520096575026477</v>
+        <v>0.752032433522587</v>
       </c>
       <c r="G10" t="n">
-        <v>28.01965316829836</v>
+        <v>28.57191225407328</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59244424512179</v>
+        <v>34.593491942039</v>
       </c>
       <c r="I10" t="n">
-        <v>3.978556159912079</v>
+        <v>3.905697746693691</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700060359391548</v>
+        <v>4.700202709516168</v>
       </c>
       <c r="K10" t="n">
-        <v>16.01027534315542</v>
+        <v>15.36505434471842</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20284410964594</v>
+        <v>43.13304288304879</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86759053393371</v>
+        <v>99.87001003251518</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.95011362716886</v>
+        <v>82.3666174216101</v>
       </c>
       <c r="C11" t="n">
-        <v>39.23163010717569</v>
+        <v>39.70968304373537</v>
       </c>
       <c r="D11" t="n">
-        <v>1.72370632552448</v>
+        <v>1.747954672920862</v>
       </c>
       <c r="E11" t="n">
-        <v>10.18223884124856</v>
+        <v>10.24662267369687</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530251645031195</v>
+        <v>0.7530243015504355</v>
       </c>
       <c r="G11" t="n">
-        <v>26.62563781230676</v>
+        <v>27.01445515400019</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63915756714349</v>
+        <v>34.63911787132003</v>
       </c>
       <c r="I11" t="n">
-        <v>3.319940638297969</v>
+        <v>3.259040863431493</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706407278144497</v>
+        <v>4.706401884690222</v>
       </c>
       <c r="K11" t="n">
-        <v>18.04988637283112</v>
+        <v>17.63338257838989</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60796807110674</v>
+        <v>42.54844277379991</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88948455111355</v>
+        <v>99.89150839592517</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.75999405126097</v>
+        <v>79.89064718448915</v>
       </c>
       <c r="C12" t="n">
-        <v>37.55559143410531</v>
+        <v>37.7387311294129</v>
       </c>
       <c r="D12" t="n">
-        <v>1.627613444742473</v>
+        <v>1.638866088177562</v>
       </c>
       <c r="E12" t="n">
-        <v>10.07623778191411</v>
+        <v>10.060296441425</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538968395774642</v>
+        <v>0.7538785668430551</v>
       </c>
       <c r="G12" t="n">
-        <v>25.14131638112306</v>
+        <v>25.32850257982</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67925462056335</v>
+        <v>34.67841407478053</v>
       </c>
       <c r="I12" t="n">
-        <v>2.769819735981368</v>
+        <v>2.718948390673915</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711855247359152</v>
+        <v>4.711741042769095</v>
       </c>
       <c r="K12" t="n">
-        <v>20.24000594873901</v>
+        <v>20.10935281551083</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11218204386963</v>
+        <v>42.06138714220317</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90777942671396</v>
+        <v>99.9094710871269</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.46582135516219</v>
+        <v>77.42820619576879</v>
       </c>
       <c r="C13" t="n">
-        <v>35.68958893681129</v>
+        <v>35.69673440847216</v>
       </c>
       <c r="D13" t="n">
-        <v>1.527787131150814</v>
+        <v>1.53137076737978</v>
       </c>
       <c r="E13" t="n">
-        <v>9.84331216891664</v>
+        <v>9.778429179780968</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546463580746816</v>
+        <v>0.7546146459578656</v>
       </c>
       <c r="G13" t="n">
-        <v>23.59932559622499</v>
+        <v>23.66717373191342</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71373247143535</v>
+        <v>34.71227371406182</v>
       </c>
       <c r="I13" t="n">
-        <v>2.310477891392969</v>
+        <v>2.268002619438274</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716539737966761</v>
+        <v>4.716341537236661</v>
       </c>
       <c r="K13" t="n">
-        <v>22.5341786448378</v>
+        <v>22.57179380423122</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69929298124031</v>
+        <v>41.65594544311122</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92306056288939</v>
+        <v>99.92447365581461</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.80673920688776</v>
+        <v>83.9920342685873</v>
       </c>
       <c r="C14" t="n">
-        <v>39.73208938417603</v>
+        <v>39.78071928621555</v>
       </c>
       <c r="D14" t="n">
-        <v>1.529478219423739</v>
+        <v>1.533137266729257</v>
       </c>
       <c r="E14" t="n">
-        <v>12.09184588253637</v>
+        <v>12.05883059212523</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554816665939935</v>
+        <v>0.7554851250799602</v>
       </c>
       <c r="G14" t="n">
-        <v>25.39926256337347</v>
+        <v>25.47915500293918</v>
       </c>
       <c r="H14" t="n">
-        <v>36.52597183513107</v>
+        <v>36.53699596352924</v>
       </c>
       <c r="I14" t="n">
-        <v>2.782938623616649</v>
+        <v>2.906648286434669</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72176041621246</v>
+        <v>4.721782031749753</v>
       </c>
       <c r="K14" t="n">
-        <v>16.19326079311225</v>
+        <v>16.00796573141271</v>
       </c>
       <c r="L14" t="n">
-        <v>43.98198776838171</v>
+        <v>44.11453834200397</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90733794566998</v>
+        <v>99.90322335963224</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.14221382083717</v>
+        <v>83.19135029343471</v>
       </c>
       <c r="C15" t="n">
-        <v>39.49806219915709</v>
+        <v>39.42962516261476</v>
       </c>
       <c r="D15" t="n">
-        <v>1.504830176278577</v>
+        <v>1.50317759464245</v>
       </c>
       <c r="E15" t="n">
-        <v>12.28386078530893</v>
+        <v>12.22727731330302</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561847509884593</v>
+        <v>0.75621906317582</v>
       </c>
       <c r="G15" t="n">
-        <v>24.98994511669992</v>
+        <v>24.98125625277346</v>
       </c>
       <c r="H15" t="n">
-        <v>36.55996450752212</v>
+        <v>36.57249089566714</v>
       </c>
       <c r="I15" t="n">
-        <v>2.321273790361286</v>
+        <v>2.42456002902394</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726154693677871</v>
+        <v>4.726369144848877</v>
       </c>
       <c r="K15" t="n">
-        <v>16.85778617916283</v>
+        <v>16.80864970656528</v>
       </c>
       <c r="L15" t="n">
-        <v>43.56684777102407</v>
+        <v>43.68098490064122</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92269614934399</v>
+        <v>99.91925976982127</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.82140151790588</v>
+        <v>80.79618041938377</v>
       </c>
       <c r="C16" t="n">
-        <v>37.53640766389478</v>
+        <v>37.40950479831936</v>
       </c>
       <c r="D16" t="n">
-        <v>1.415899159849612</v>
+        <v>1.411349485863954</v>
       </c>
       <c r="E16" t="n">
-        <v>11.88057746846768</v>
+        <v>11.81734654288</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756788521678189</v>
+        <v>0.7568499470038913</v>
       </c>
       <c r="G16" t="n">
-        <v>23.51311320917658</v>
+        <v>23.45516810139384</v>
       </c>
       <c r="H16" t="n">
-        <v>36.58915556824948</v>
+        <v>36.60300188670387</v>
       </c>
       <c r="I16" t="n">
-        <v>1.935939329995665</v>
+        <v>2.022152286763895</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729928260488682</v>
+        <v>4.730312168774323</v>
       </c>
       <c r="K16" t="n">
-        <v>19.17859848209412</v>
+        <v>19.20381958061622</v>
       </c>
       <c r="L16" t="n">
-        <v>43.22051402650106</v>
+        <v>43.3193267313693</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93552017248996</v>
+        <v>99.93265111030487</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.34416092953199</v>
+        <v>82.34667420365486</v>
       </c>
       <c r="C17" t="n">
-        <v>38.66905005648819</v>
+        <v>38.55048623700268</v>
       </c>
       <c r="D17" t="n">
-        <v>1.416988821471424</v>
+        <v>1.412497831082582</v>
       </c>
       <c r="E17" t="n">
-        <v>12.59990886754039</v>
+        <v>12.54980282825255</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573709384429455</v>
+        <v>0.7574657583437232</v>
       </c>
       <c r="G17" t="n">
-        <v>23.92454073745973</v>
+        <v>23.86208644182906</v>
       </c>
       <c r="H17" t="n">
-        <v>37.01064628600821</v>
+        <v>37.02061796870765</v>
       </c>
       <c r="I17" t="n">
-        <v>1.901136913340878</v>
+        <v>2.010042385791023</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73356836526841</v>
+        <v>4.734160989648273</v>
       </c>
       <c r="K17" t="n">
-        <v>17.65583907046802</v>
+        <v>17.65332579634515</v>
       </c>
       <c r="L17" t="n">
-        <v>43.61178837495091</v>
+        <v>43.72924102520503</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93667750190711</v>
+        <v>99.93305305855287</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.09567397997256</v>
+        <v>80.01365877675977</v>
       </c>
       <c r="C18" t="n">
-        <v>36.71436920887464</v>
+        <v>36.52800998619493</v>
       </c>
       <c r="D18" t="n">
-        <v>1.333894651422908</v>
+        <v>1.326300203368916</v>
       </c>
       <c r="E18" t="n">
-        <v>12.12525391354062</v>
+        <v>12.0633190761173</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578706241269774</v>
+        <v>0.7579946963230864</v>
       </c>
       <c r="G18" t="n">
-        <v>22.52157281968408</v>
+        <v>22.40590350241339</v>
       </c>
       <c r="H18" t="n">
-        <v>37.03506455870284</v>
+        <v>37.04646944865568</v>
       </c>
       <c r="I18" t="n">
-        <v>1.585326011701538</v>
+        <v>1.676204997862114</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73669140079361</v>
+        <v>4.737466852019293</v>
       </c>
       <c r="K18" t="n">
-        <v>19.90432602002745</v>
+        <v>19.98634122324023</v>
       </c>
       <c r="L18" t="n">
-        <v>43.32849541239402</v>
+        <v>43.42981427984844</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94719064129609</v>
+        <v>99.94416548928359</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.18734136904931</v>
+        <v>79.03583806332992</v>
       </c>
       <c r="C19" t="n">
-        <v>36.05044356614323</v>
+        <v>35.80850301449594</v>
       </c>
       <c r="D19" t="n">
-        <v>1.300943974231388</v>
+        <v>1.290830315907493</v>
       </c>
       <c r="E19" t="n">
-        <v>12.04603519756494</v>
+        <v>11.97364738310974</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582923176967007</v>
+        <v>0.758441506091867</v>
       </c>
       <c r="G19" t="n">
-        <v>21.96523122626433</v>
+        <v>21.80669159421686</v>
       </c>
       <c r="H19" t="n">
-        <v>37.05567157008646</v>
+        <v>37.06830696879769</v>
       </c>
       <c r="I19" t="n">
-        <v>1.321840097601115</v>
+        <v>1.397660882132103</v>
       </c>
       <c r="J19" t="n">
-        <v>4.73932698560438</v>
+        <v>4.740259413074172</v>
       </c>
       <c r="K19" t="n">
-        <v>20.81265863095068</v>
+        <v>20.96416193667005</v>
       </c>
       <c r="L19" t="n">
-        <v>43.09286096924773</v>
+        <v>43.18077379889341</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95596316634165</v>
+        <v>99.95343875005941</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.72988942064093</v>
+        <v>76.46124397885086</v>
       </c>
       <c r="C20" t="n">
-        <v>33.79663966979359</v>
+        <v>33.44913628180967</v>
       </c>
       <c r="D20" t="n">
-        <v>1.210988009286151</v>
+        <v>1.196677367132819</v>
       </c>
       <c r="E20" t="n">
-        <v>11.39676857784147</v>
+        <v>11.29450971543751</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586553592853087</v>
+        <v>0.7588268075167712</v>
       </c>
       <c r="G20" t="n">
-        <v>20.44640827205429</v>
+        <v>20.21611513245166</v>
       </c>
       <c r="H20" t="n">
-        <v>37.07341241957126</v>
+        <v>37.08713831093699</v>
       </c>
       <c r="I20" t="n">
-        <v>1.102060787069284</v>
+        <v>1.165309098395293</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741595995533181</v>
+        <v>4.742667546979823</v>
       </c>
       <c r="K20" t="n">
-        <v>23.27011057935905</v>
+        <v>23.53875602114914</v>
       </c>
       <c r="L20" t="n">
-        <v>42.89653197035843</v>
+        <v>42.97328378364862</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96328221951107</v>
+        <v>99.96117608660742</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.09215611132886</v>
+        <v>82.14015375658948</v>
       </c>
       <c r="C21" t="n">
-        <v>37.16411525885756</v>
+        <v>36.9829298453807</v>
       </c>
       <c r="D21" t="n">
-        <v>1.211732455458633</v>
+        <v>1.19747996076509</v>
       </c>
       <c r="E21" t="n">
-        <v>13.20661617879936</v>
+        <v>13.19938995363715</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759121737213184</v>
+        <v>0.7593357413200144</v>
       </c>
       <c r="G21" t="n">
-        <v>22.00949126005562</v>
+        <v>21.85152808819608</v>
       </c>
       <c r="H21" t="n">
-        <v>38.64671673883478</v>
+        <v>38.73386640988112</v>
       </c>
       <c r="I21" t="n">
-        <v>1.513966883384887</v>
+        <v>1.652705219539934</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744510857582402</v>
+        <v>4.745848383250093</v>
       </c>
       <c r="K21" t="n">
-        <v>17.90784388867113</v>
+        <v>17.85984624341051</v>
       </c>
       <c r="L21" t="n">
-        <v>44.87760629397405</v>
+        <v>45.10217066061684</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94956544150274</v>
+        <v>99.94494674940805</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_64_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.71413580552456</v>
+        <v>43.72098644130644</v>
       </c>
       <c r="M2" t="n">
-        <v>99.54154433379179</v>
+        <v>95.72544363019566</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.12228768149052</v>
+        <v>81.50302463518993</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9582034769162</v>
+        <v>43.2585801907455</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228951652950608</v>
+        <v>2.181870016658651</v>
       </c>
       <c r="E3" t="n">
-        <v>5.728456045212723</v>
+        <v>4.148707951882404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429838843168693</v>
+        <v>0.7376514107298987</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98236408690011</v>
+        <v>32.81896150057388</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17725867857599</v>
+        <v>33.93196489357533</v>
       </c>
       <c r="I3" t="n">
-        <v>6.618624056553783</v>
+        <v>3.073547544707911</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643649276980433</v>
+        <v>4.610321317061866</v>
       </c>
       <c r="K3" t="n">
-        <v>11.8777123185095</v>
+        <v>18.49697536481006</v>
       </c>
       <c r="L3" t="n">
-        <v>48.92653310120095</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7624488966266</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.38164883897515</v>
+        <v>88.59548706291062</v>
       </c>
       <c r="C4" t="n">
-        <v>42.86137016805299</v>
+        <v>42.9192607490167</v>
       </c>
       <c r="D4" t="n">
-        <v>2.194205899423028</v>
+        <v>2.187552191437899</v>
       </c>
       <c r="E4" t="n">
-        <v>6.560350199368851</v>
+        <v>6.570700449839107</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445504156569606</v>
+        <v>0.7395724528680298</v>
       </c>
       <c r="G4" t="n">
-        <v>33.45263395781235</v>
+        <v>33.53320892234866</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24931912022019</v>
+        <v>34.02033283192936</v>
       </c>
       <c r="I4" t="n">
-        <v>5.527149148637766</v>
+        <v>6.921792384062393</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653440097856003</v>
+        <v>4.622327830425185</v>
       </c>
       <c r="K4" t="n">
-        <v>12.61835116102484</v>
+        <v>11.40451293708936</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33642800268458</v>
+        <v>45.44609921378889</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81614933176242</v>
+        <v>99.76987289989495</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.38582301176038</v>
+        <v>87.3521038919415</v>
       </c>
       <c r="C5" t="n">
-        <v>42.72357424902388</v>
+        <v>42.74901089886654</v>
       </c>
       <c r="D5" t="n">
-        <v>2.146250849089668</v>
+        <v>2.127921221396029</v>
       </c>
       <c r="E5" t="n">
-        <v>7.185998091760021</v>
+        <v>7.355069055107303</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458760473199801</v>
+        <v>0.7412039278201799</v>
       </c>
       <c r="G5" t="n">
-        <v>32.72151626933463</v>
+        <v>32.61911974793588</v>
       </c>
       <c r="H5" t="n">
-        <v>34.31029817671909</v>
+        <v>34.09538067972827</v>
       </c>
       <c r="I5" t="n">
-        <v>4.614158281787122</v>
+        <v>5.780884711077724</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661725295749875</v>
+        <v>4.632524548876123</v>
       </c>
       <c r="K5" t="n">
-        <v>13.61417698823961</v>
+        <v>12.6478961080585</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50871684194099</v>
+        <v>44.41082098240654</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8464680792045</v>
+        <v>99.80772798933158</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.22453317163421</v>
+        <v>85.75825023396882</v>
       </c>
       <c r="C6" t="n">
-        <v>42.27920673429298</v>
+        <v>42.05236094860306</v>
       </c>
       <c r="D6" t="n">
-        <v>2.090126789959931</v>
+        <v>2.05120563709701</v>
       </c>
       <c r="E6" t="n">
-        <v>7.639906147928182</v>
+        <v>7.894311791603169</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469994763804996</v>
+        <v>0.7425944168788466</v>
       </c>
       <c r="G6" t="n">
-        <v>31.86585472600025</v>
+        <v>31.44313879261608</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36197591350298</v>
+        <v>34.15934317642694</v>
       </c>
       <c r="I6" t="n">
-        <v>3.850923390484236</v>
+        <v>4.826441313853993</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668746727378122</v>
+        <v>4.641215105492791</v>
       </c>
       <c r="K6" t="n">
-        <v>14.7754668283658</v>
+        <v>14.24174976603118</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81715537395823</v>
+        <v>43.54530915450249</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87182893661702</v>
+        <v>99.83941986913672</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.87106773568762</v>
+        <v>83.98176740218746</v>
       </c>
       <c r="C7" t="n">
-        <v>41.52427217522285</v>
+        <v>41.02510687778233</v>
       </c>
       <c r="D7" t="n">
-        <v>2.024699642210425</v>
+        <v>1.966302831735571</v>
       </c>
       <c r="E7" t="n">
-        <v>7.936287995266506</v>
+        <v>8.238964031992738</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479534245109136</v>
+        <v>0.7437817841036138</v>
       </c>
       <c r="G7" t="n">
-        <v>30.86835926527641</v>
+        <v>30.14165509708549</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40585752750203</v>
+        <v>34.21396206876623</v>
       </c>
       <c r="I7" t="n">
-        <v>3.213200977728125</v>
+        <v>4.028465437856219</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67470890319321</v>
+        <v>4.648636150647586</v>
       </c>
       <c r="K7" t="n">
-        <v>16.1289322643124</v>
+        <v>16.01823259781256</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23982546628463</v>
+        <v>42.82259271013139</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89302990581987</v>
+        <v>99.86593218572628</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.63978639590285</v>
+        <v>82.02337034132189</v>
       </c>
       <c r="C8" t="n">
-        <v>43.77906414573303</v>
+        <v>39.691815772643</v>
       </c>
       <c r="D8" t="n">
-        <v>2.028967640848737</v>
+        <v>1.873416406133587</v>
       </c>
       <c r="E8" t="n">
-        <v>9.735370270709634</v>
+        <v>8.410036030213538</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495300851329544</v>
+        <v>0.7447978876496382</v>
       </c>
       <c r="G8" t="n">
-        <v>31.35748094144507</v>
+        <v>28.71778967894698</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4783839161159</v>
+        <v>34.26070283188335</v>
       </c>
       <c r="I8" t="n">
-        <v>5.605490509569599</v>
+        <v>3.36164070868456</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684563032080964</v>
+        <v>4.654986797810237</v>
       </c>
       <c r="K8" t="n">
-        <v>11.36021360409715</v>
+        <v>17.97662965867811</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67426561083195</v>
+        <v>42.21965275096066</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81354336066212</v>
+        <v>99.88809818228178</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.77864147458159</v>
+        <v>79.87428687425026</v>
       </c>
       <c r="C9" t="n">
-        <v>42.78874436536648</v>
+        <v>38.06385107874495</v>
       </c>
       <c r="D9" t="n">
-        <v>1.944886793994464</v>
+        <v>1.772257536123224</v>
       </c>
       <c r="E9" t="n">
-        <v>10.11187427885109</v>
+        <v>8.4233603110159</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508773944211348</v>
+        <v>0.7456696302210225</v>
       </c>
       <c r="G9" t="n">
-        <v>30.05802031935722</v>
+        <v>27.16711512330291</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5403601433722</v>
+        <v>34.30080299016703</v>
       </c>
       <c r="I9" t="n">
-        <v>4.679638829453395</v>
+        <v>2.804646094538784</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692983715132092</v>
+        <v>4.660435188881389</v>
       </c>
       <c r="K9" t="n">
-        <v>13.2213585254184</v>
+        <v>20.12571312574975</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83418903950487</v>
+        <v>41.71705688693072</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84429193028974</v>
+        <v>99.90662109142542</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.63494565528157</v>
+        <v>85.18353236984642</v>
       </c>
       <c r="C10" t="n">
-        <v>41.37191280474796</v>
+        <v>41.61202612503669</v>
       </c>
       <c r="D10" t="n">
-        <v>1.848729032441617</v>
+        <v>1.774346685684082</v>
       </c>
       <c r="E10" t="n">
-        <v>10.26287953699524</v>
+        <v>10.43820399428296</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752032433522587</v>
+        <v>0.7465486307888118</v>
       </c>
       <c r="G10" t="n">
-        <v>28.57191225407328</v>
+        <v>28.70197936129141</v>
       </c>
       <c r="H10" t="n">
-        <v>34.593491942039</v>
+        <v>35.84407646923399</v>
       </c>
       <c r="I10" t="n">
-        <v>3.905697746693691</v>
+        <v>3.012448286135101</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700202709516168</v>
+        <v>4.665928942430073</v>
       </c>
       <c r="K10" t="n">
-        <v>15.36505434471842</v>
+        <v>14.81646763015356</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13304288304879</v>
+        <v>43.47120953240363</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87001003251518</v>
+        <v>99.89970328759389</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.3666174216101</v>
+        <v>84.59207846542296</v>
       </c>
       <c r="C11" t="n">
-        <v>39.70968304373537</v>
+        <v>41.37436915806127</v>
       </c>
       <c r="D11" t="n">
-        <v>1.747954672920862</v>
+        <v>1.739365127012886</v>
       </c>
       <c r="E11" t="n">
-        <v>10.24662267369687</v>
+        <v>10.72600919906667</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530243015504355</v>
+        <v>0.7473011000921361</v>
       </c>
       <c r="G11" t="n">
-        <v>27.01445515400019</v>
+        <v>28.20339622982726</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63911787132003</v>
+        <v>35.94748628234658</v>
       </c>
       <c r="I11" t="n">
-        <v>3.259040863431493</v>
+        <v>2.55788865150157</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706401884690222</v>
+        <v>4.67063187557585</v>
       </c>
       <c r="K11" t="n">
-        <v>17.63338257838989</v>
+        <v>15.40792153457706</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54844277379991</v>
+        <v>43.13253220493029</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89150839592517</v>
+        <v>99.91482289756861</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.89064718448915</v>
+        <v>82.28438231182038</v>
       </c>
       <c r="C12" t="n">
-        <v>37.7387311294129</v>
+        <v>39.46363781510495</v>
       </c>
       <c r="D12" t="n">
-        <v>1.638866088177562</v>
+        <v>1.642085067974712</v>
       </c>
       <c r="E12" t="n">
-        <v>10.060296441425</v>
+        <v>10.48168908469497</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538785668430551</v>
+        <v>0.7479469513612552</v>
       </c>
       <c r="G12" t="n">
-        <v>25.32850257982</v>
+        <v>26.62602296431491</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67841407478053</v>
+        <v>35.97855371906551</v>
       </c>
       <c r="I12" t="n">
-        <v>2.718948390673915</v>
+        <v>2.133416078401189</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711741042769095</v>
+        <v>4.674668446007844</v>
       </c>
       <c r="K12" t="n">
-        <v>20.10935281551083</v>
+        <v>17.71561768817961</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06138714220317</v>
+        <v>42.74969203417374</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9094710871269</v>
+        <v>99.9289475374583</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.42820619576879</v>
+        <v>83.45548951326231</v>
       </c>
       <c r="C13" t="n">
-        <v>35.69673440847216</v>
+        <v>40.42904627211951</v>
       </c>
       <c r="D13" t="n">
-        <v>1.53137076737978</v>
+        <v>1.643403096501223</v>
       </c>
       <c r="E13" t="n">
-        <v>9.778429179780968</v>
+        <v>11.12359213721514</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546146459578656</v>
+        <v>0.7485472950568636</v>
       </c>
       <c r="G13" t="n">
-        <v>23.66717373191342</v>
+        <v>26.94595433760935</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71227371406182</v>
+        <v>36.30599195212638</v>
       </c>
       <c r="I13" t="n">
-        <v>2.268002619438274</v>
+        <v>2.00958010064796</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716341537236661</v>
+        <v>4.678420594105396</v>
       </c>
       <c r="K13" t="n">
-        <v>22.57179380423122</v>
+        <v>16.54451048673767</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65594544311122</v>
+        <v>42.95951096134693</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92447365581461</v>
+        <v>99.93306772020412</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.9920342685873</v>
+        <v>81.11638725060094</v>
       </c>
       <c r="C14" t="n">
-        <v>39.78071928621555</v>
+        <v>38.40150295103339</v>
       </c>
       <c r="D14" t="n">
-        <v>1.533137266729257</v>
+        <v>1.547671316880314</v>
       </c>
       <c r="E14" t="n">
-        <v>12.05883059212523</v>
+        <v>10.7549194245574</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554851250799602</v>
+        <v>0.7490627757888584</v>
       </c>
       <c r="G14" t="n">
-        <v>25.47915500293918</v>
+        <v>25.37629430239645</v>
       </c>
       <c r="H14" t="n">
-        <v>36.53699596352924</v>
+        <v>36.33099376487871</v>
       </c>
       <c r="I14" t="n">
-        <v>2.906648286434669</v>
+        <v>1.675803317418824</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721782031749753</v>
+        <v>4.681642348680364</v>
       </c>
       <c r="K14" t="n">
-        <v>16.00796573141271</v>
+        <v>18.88361274939908</v>
       </c>
       <c r="L14" t="n">
-        <v>44.11453834200397</v>
+        <v>42.65906263010508</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90322335963224</v>
+        <v>99.94417833053754</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.19135029343471</v>
+        <v>80.07071795333061</v>
       </c>
       <c r="C15" t="n">
-        <v>39.42962516261476</v>
+        <v>37.58088352524392</v>
       </c>
       <c r="D15" t="n">
-        <v>1.50317759464245</v>
+        <v>1.503986442053431</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22727731330302</v>
+        <v>10.68974862340786</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75621906317582</v>
+        <v>0.7495088222891187</v>
       </c>
       <c r="G15" t="n">
-        <v>24.98125625277346</v>
+        <v>24.66001803102064</v>
       </c>
       <c r="H15" t="n">
-        <v>36.57249089566714</v>
+        <v>36.35262788306426</v>
       </c>
       <c r="I15" t="n">
-        <v>2.42456002902394</v>
+        <v>1.430398012188306</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726369144848877</v>
+        <v>4.684430139306992</v>
       </c>
       <c r="K15" t="n">
-        <v>16.80864970656528</v>
+        <v>19.9292820466694</v>
       </c>
       <c r="L15" t="n">
-        <v>43.68098490064122</v>
+        <v>42.44218286955353</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91925976982127</v>
+        <v>99.95234844146685</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.79618041938377</v>
+        <v>77.44024278952578</v>
       </c>
       <c r="C16" t="n">
-        <v>37.40950479831936</v>
+        <v>35.17145314554794</v>
       </c>
       <c r="D16" t="n">
-        <v>1.411349485863954</v>
+        <v>1.397354796191061</v>
       </c>
       <c r="E16" t="n">
-        <v>11.81734654288</v>
+        <v>10.13062087827767</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568499470038913</v>
+        <v>0.7498935799951681</v>
       </c>
       <c r="G16" t="n">
-        <v>23.45516810139384</v>
+        <v>22.91163903230222</v>
       </c>
       <c r="H16" t="n">
-        <v>36.60300188670387</v>
+        <v>36.37128937616108</v>
       </c>
       <c r="I16" t="n">
-        <v>2.022152286763895</v>
+        <v>1.192610251628782</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730312168774323</v>
+        <v>4.6868348749698</v>
       </c>
       <c r="K16" t="n">
-        <v>19.20381958061622</v>
+        <v>22.55975721047422</v>
       </c>
       <c r="L16" t="n">
-        <v>43.3193267313693</v>
+        <v>42.2290563658615</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93265111030487</v>
+        <v>99.96026672188366</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.34667420365486</v>
+        <v>82.95373789657587</v>
       </c>
       <c r="C17" t="n">
-        <v>38.55048623700268</v>
+        <v>38.78346530613824</v>
       </c>
       <c r="D17" t="n">
-        <v>1.412497831082582</v>
+        <v>1.398132562932407</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54980282825255</v>
+        <v>12.0496682688154</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574657583437232</v>
+        <v>0.7503109702582986</v>
       </c>
       <c r="G17" t="n">
-        <v>23.86208644182906</v>
+        <v>24.60694035488148</v>
       </c>
       <c r="H17" t="n">
-        <v>37.02061796870765</v>
+        <v>38.07408233108463</v>
       </c>
       <c r="I17" t="n">
-        <v>2.010042385791023</v>
+        <v>1.385159844489287</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734160989648273</v>
+        <v>4.689443564114366</v>
       </c>
       <c r="K17" t="n">
-        <v>17.65332579634515</v>
+        <v>17.04626210342413</v>
       </c>
       <c r="L17" t="n">
-        <v>43.72924102520503</v>
+        <v>44.12412628062638</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93305305855287</v>
+        <v>99.95385369018877</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.01365877675977</v>
+        <v>84.67423111331432</v>
       </c>
       <c r="C18" t="n">
-        <v>36.52800998619493</v>
+        <v>39.53725373894851</v>
       </c>
       <c r="D18" t="n">
-        <v>1.326300203368916</v>
+        <v>1.399397906967885</v>
       </c>
       <c r="E18" t="n">
-        <v>12.0633190761173</v>
+        <v>12.67687007754366</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579946963230864</v>
+        <v>0.7509900199679908</v>
       </c>
       <c r="G18" t="n">
-        <v>22.40590350241339</v>
+        <v>24.74577791244275</v>
       </c>
       <c r="H18" t="n">
-        <v>37.04646944865568</v>
+        <v>38.10854030328357</v>
       </c>
       <c r="I18" t="n">
-        <v>1.676204997862114</v>
+        <v>2.298967268308528</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737466852019293</v>
+        <v>4.693687624799941</v>
       </c>
       <c r="K18" t="n">
-        <v>19.98634122324023</v>
+        <v>15.32576888668568</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42981427984844</v>
+        <v>45.06041442342493</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94416548928359</v>
+        <v>99.92343704905913</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.03583806332992</v>
+        <v>81.75485705258079</v>
       </c>
       <c r="C19" t="n">
-        <v>35.80850301449594</v>
+        <v>36.97296286567605</v>
       </c>
       <c r="D19" t="n">
-        <v>1.290830315907493</v>
+        <v>1.295176448683795</v>
       </c>
       <c r="E19" t="n">
-        <v>11.97364738310974</v>
+        <v>12.05229902593031</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758441506091867</v>
+        <v>0.7515770904671523</v>
       </c>
       <c r="G19" t="n">
-        <v>21.80669159421686</v>
+        <v>22.90281312911169</v>
       </c>
       <c r="H19" t="n">
-        <v>37.06830696879769</v>
+        <v>38.13833084534579</v>
       </c>
       <c r="I19" t="n">
-        <v>1.397660882132103</v>
+        <v>1.917303697622359</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740259413074172</v>
+        <v>4.697356815419701</v>
       </c>
       <c r="K19" t="n">
-        <v>20.96416193667005</v>
+        <v>18.24514294741921</v>
       </c>
       <c r="L19" t="n">
-        <v>43.18077379889341</v>
+        <v>44.71803398500728</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95343875005941</v>
+        <v>99.93613979810254</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.46124397885086</v>
+        <v>78.78879107103329</v>
       </c>
       <c r="C20" t="n">
-        <v>33.44913628180967</v>
+        <v>34.30209189287077</v>
       </c>
       <c r="D20" t="n">
-        <v>1.196677367132819</v>
+        <v>1.190007107395003</v>
       </c>
       <c r="E20" t="n">
-        <v>11.29450971543751</v>
+        <v>11.34011521850413</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588268075167712</v>
+        <v>0.7520854736464613</v>
       </c>
       <c r="G20" t="n">
-        <v>20.21611513245166</v>
+        <v>21.04308677839186</v>
       </c>
       <c r="H20" t="n">
-        <v>37.08713831093699</v>
+        <v>38.16412844632994</v>
       </c>
       <c r="I20" t="n">
-        <v>1.165309098395293</v>
+        <v>1.598833836475493</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742667546979823</v>
+        <v>4.700534210290383</v>
       </c>
       <c r="K20" t="n">
-        <v>23.53875602114914</v>
+        <v>21.21120892896671</v>
       </c>
       <c r="L20" t="n">
-        <v>42.97328378364862</v>
+        <v>44.43344074211746</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96117608660742</v>
+        <v>99.94674156395494</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.14015375658948</v>
+        <v>75.82405044888651</v>
       </c>
       <c r="C21" t="n">
-        <v>36.9829298453807</v>
+        <v>31.58261421085672</v>
       </c>
       <c r="D21" t="n">
-        <v>1.19747996076509</v>
+        <v>1.085557298235313</v>
       </c>
       <c r="E21" t="n">
-        <v>13.19938995363715</v>
+        <v>10.56695620759655</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593357413200144</v>
+        <v>0.7525262471725438</v>
       </c>
       <c r="G21" t="n">
-        <v>21.85152808819608</v>
+        <v>19.19608402985764</v>
       </c>
       <c r="H21" t="n">
-        <v>38.73386640988112</v>
+        <v>38.18649523581677</v>
       </c>
       <c r="I21" t="n">
-        <v>1.652705219539934</v>
+        <v>1.333142385379285</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745848383250093</v>
+        <v>4.703289044828398</v>
       </c>
       <c r="K21" t="n">
-        <v>17.85984624341051</v>
+        <v>24.17594955111349</v>
       </c>
       <c r="L21" t="n">
-        <v>45.10217066061684</v>
+        <v>44.19702418701657</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94494674940805</v>
+        <v>99.95558794898677</v>
       </c>
     </row>
   </sheetData>
